--- a/output/teachers.xlsx
+++ b/output/teachers.xlsx
@@ -63,25 +63,60 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>direction_tags</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>relevance_score</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ai_cv_keywords</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>research_plain_explanation</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>recommendation_priority</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>来源URL</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>发现来源URL</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>原始HTML路径</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>原始文本路径</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>抓取状态</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -95,12 +130,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>教授研究员</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>待人工核验</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -110,55 +145,90 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>待人工核验</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>待人工核验</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>待人工核验</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>待人工核验</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>待人工核验</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>待人工核验</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>当前主页抓取失败，无法判断方向。</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>https://faculty.hust.edu.cn/hufei/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>data\raw_html\胡飞_5c59fb2916.html</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>data\raw_text\胡飞_5c59fb2916.txt</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>请求或解析失败：&lt;urlopen error _ssl.c:1063: The handshake operation timed out&gt;</t>
         </is>
@@ -217,25 +287,60 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>通信/信号处理；电磁/微波；遥感/雷达</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>偏遥感/雷达成像与智能处理，可能存在 CV 方法和信号处理结合点。</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/liqingxia/</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>data\raw_html\李青侠_1757adb48b.html</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>data\raw_text\李青侠_1757adb48b.txt</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -294,25 +399,60 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>通信/信号处理；电磁/微波；遥感/雷达；硬件/嵌入式；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>偏遥感/雷达成像与智能处理，可能存在 CV 方法和信号处理结合点。</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/mahong/</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>data\raw_html\马洪_3d1a91e8a5.html</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>data\raw_text\马洪_3d1a91e8a5.txt</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -371,25 +511,60 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>AI/机器学习；通信/信号处理；电磁/微波；遥感/雷达；硬件/嵌入式</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>深度学习</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>偏智能算法或机器学习应用方向，需要人工核验是否是真正的 AI/CV 课题。</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/chenping9/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>data\raw_html\陈萍_32ff71596a.html</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>data\raw_text\陈萍_32ff71596a.txt</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -448,25 +623,60 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>CV/图像处理；AI/机器学习；通信/信号处理；遥感/雷达；光电/激光</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>图像处理；智能感知；多模态；detection</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>偏视觉/图像与智能算法交叉，可重点看是否有检测、识别、分割、多模态或深度学习课题。</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/liangkun/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>data\raw_html\梁琨_50d58e9f68.html</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>data\raw_text\梁琨_50d58e9f68.txt</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -525,25 +735,60 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>通信/信号处理；电磁/微波；遥感/雷达</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>偏遥感/雷达成像与智能处理，可能存在 CV 方法和信号处理结合点。</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/chenke/index.htm</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>data\raw_html\陈柯_6a62404523.html</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>data\raw_text\陈柯_6a62404523.txt</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -557,7 +802,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>副教授副研究员</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -602,25 +847,60 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/hefeng/</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>data\raw_html\贺锋_0dce7760f1.html</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>data\raw_text\贺锋_0dce7760f1.txt</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>页面可读取文本较少，建议人工打开原始HTML或来源URL核验。</t>
         </is>
@@ -679,27 +959,7678 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>通信/信号处理；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/zhangjing/</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>data\raw_html\张靖_14714bfbf4.html</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>data\raw_text\张靖_14714bfbf4.txt</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>周波</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>电子工程系</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>zhoubo@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>周波，男，博士，华中科技大学电子信息与通信学院副教授。；个人网站；http://xxxxxx；个人邮箱；zhoubo@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>代表性；• Zhou Bo, Wang Shengqing, Ma Yong, Mei Xiaoguang, Li Bin, Li；Hao, Fan Fan, An infrared image impulse noise suppression algorithm based on；fuzzy logic, INFR</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>CV/图像处理；通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>image；vision</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>偏图像、视频、视觉感知或成像处理方向，适合从论文复现和数据处理切入。</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/zhoubo/</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>data\raw_html\周波_ea883f9c1a.html</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>data\raw_text\周波_ea883f9c1a.txt</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>田加胜</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>电子工程系</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Tianjs@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>田加胜，男，博士，华中科技大学电子信息与通信学院副教授；个人网站；********；电子邮箱；Tianjs@hust.edu.cn；主要研究领域；微波遥感与探测、电磁理论与应用、电磁场数值计算、天线理论与技术</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>招收研究生：08090401；微波、毫米波技术及应用；08090403无源探测理论与技术；08090404微波遥感与成像；08090405 电磁理论与应用；主要著作；著作名称：微波技术基础，出版时间2011.1.1，出版社：华中科技大学出版社。</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>国家自然科学基金项目；国防863项目；CAST项目；湖北省自然科学基金项目；基于电磁带隙技术的纤维束天线的应用基础研究；其他横向项目；集成天线仿真与分析；主要论文；一种充分考虑高海况的风速反演算法研究</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；硬件测试、仿真建模、实验平台辅助</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>通信/信号处理；电磁/微波；遥感/雷达</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>偏遥感/雷达成像与智能处理，可能存在 CV 方法和信号处理结合点。</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/tianjiasheng</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>data\raw_html\田加胜_3e108a8f19.html</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>data\raw_text\田加胜_3e108a8f19.txt</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>金江</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>硕士生导师</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>电子工程系</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>jinjiang@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>金江，通信与信息系统专业博士，华中科技大学电子信息与通信学院副教授、硕士生导师。涉及：无线通信、移动通信与光通信；信号处理技术；电子对抗与雷达；软件无线电；现代电子设备与系统设计；微弱信号检测与处理。；主要承担研究项目；“抗截获破译的××××传输链路新技术”，武器装备教育部联合预研基金项目;；“新型××××接收机技术”,“十二.五”国防预研项目；；“基于非线性变换对的新型信道加密和多址技术”,自主研发基金;；“基于短波广播信号的××××技术”,航天基金支撑项目；；“大动态射频××××技术研究”,“十一.五”预研项目，参与;；“THz空间通信系统关键技术研究”,CAST航天创新基金项目;；“大动态盲辨识接收机信号处理技术”, 自主研发基金;；“雷电灾害监测预警关键技术研究与系统研发”，“十二五”国家科技支撑计划重点项目,参与；；“隐身目标探测××××提升技术研究”,SAST航天创新基金；；“基于××××技术”，“十三.五”预研项目</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>通信/信号处理；电磁/微波；遥感/雷达；信息安全</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>偏遥感/雷达成像与智能处理，可能存在 CV 方法和信号处理结合点。</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/jinjiang/</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>data\raw_html\金江_557bafb51e.html</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>data\raw_text\金江_557bafb51e.txt</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>黄全亮</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>电子工程系</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>huangql@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>姓名:黄全亮；电子信息与通信学院副教授；个人简介</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>黄全亮，男，博士，华中科技大学电子信息与通信学院副教授。分别于1997年和2002年获得华中科技大学材料物理专业硕士学位和电磁场与微波技术博士学位，2006年9月华中科技大学控制系统与控制工程博士后流动站出站。2017年赴法国图卢兹大学访学一年。现为毫米波辐射成像和遥感图像信息处理。主持两项国家自然科学基金面上项目，在国内外学术会议、期刊上发表论文多篇。；个人邮箱：huangql@hust.edu.cn；承担课程；• 阵列信号处理；• 电磁场与无线技术专业课程设计；承担课题情况；• 主持国际自然科学基金“超分辨率技术在无源微波制导中的应用研究”，2008.01-2010.12；• 主持国际自然科学基金“基于延时相关的综合孔径辐射计研究”，2017.01-2020.12</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>华中科技大学电子信息与通信学院副教授；现主要研究方向为毫米波辐射成像和遥感图像信息处理；主持两项国家自然科学基金面上项目；阵列信号处理；主持国际自然科学基金；代表性性论文</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>CV/图像处理；通信/信号处理；电磁/微波；遥感/雷达</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>偏图像、视频、视觉感知或成像处理方向，适合从论文复现和数据处理切入。</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/huangquanliang/</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>data\raw_html\黄全亮_1481165afe.html</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>data\raw_text\黄全亮_1481165afe.txt</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>张华</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>电子工程系</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>zhanghua@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>张华，男，博士，华中科技大学电子信息与通信学院副教授</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>目标探测与定位、无线电监测、软件无线电</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>主要；l Nonlinear Blind；Compensation for Array Signal Processing Application[J]. Sensors,2018,；18(4)；l A Nonlinearity Mitigation Method for a Broadband RF Front-En</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>通信/信号处理；遥感/雷达</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/zhanghua/</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>data\raw_html\张华_8455ae09ee.html</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>data\raw_text\张华_8455ae09ee.txt</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>朱冬</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>副教授副研究员</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>电子工程系</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>detection；image</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/zhudong/</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>data\raw_html\朱冬_6744056529.html</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>data\raw_text\朱冬_6744056529.txt</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>刘明罡</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>研究员</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>电子工程系</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>liuminggang@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1. 个人简介；刘明罡，博士。2003年，毕业于华中科技大学电子信息工程系，获得学士学位，2009年1月，毕业于清华大学电子工程系，获得博士学位。2009年2月，入职中国电科第14研究所， 2014年～2017年，任天线微波专业部阵面系统室副主任。2019年，获得研究员级高级工程师资格。2022年9月，入职华中科技大学电子信息与通信学院电子工程系。；刘明罡博士长期从事大型高频精密测量雷达有源相控阵天线、毫米波导引头天线、低成本芯片化相控阵天线、舰载综合射频系统多功能共孔径相控阵天线、相控阵天线隐身、固态高功率微波等相关技术的研究和产品开发工作，完成了一系列服务于我国军工科研生产、军民融合产业的重点项目。；邮箱：liuminggang@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2.；相控阵天线系统、分布式阵列天线技术、低成本相控阵天线、相控阵阵馈源技术、相控阵天线标校与自动化测试、隐身与电磁兼容技术等。；3. 项目经历；[1] 某大型高频段全有源相控阵天线系统。在该项目中，提出了大单元间距稀疏阵相控阵天线架构，减少了70%的天线单元数量和TR组件；同时采用非周期化方法，有效抑制天线阵列栅瓣。研究大型天线阵面结构变形的电讯补偿方法，有效克服阵面重力形变带来的指向误差。；[2] 低成本芯片化相控阵天线：研制了基于芯片化TR组件的X波段相控阵天线样机。通过综合网络技术，实现了芯片化TR组件、电源、馈电网络、控制电路的一体化集成。；[3] 综合射频多功能共孔径相控阵天线：研制近万对双极化天线单元的多倍频程的有源相控阵天线，，具备同时双极化接收与分时双极化发射能力，每路天线单元具备双路独立射频通道，并可实现宽带数字多波束。；[4] 相控阵天线隐身技术研究：研究了相控阵天线阵列的电磁散射特性，提出了降低相控阵天线</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>扁波导馈电的平板缝隙天线阵的带宽扩展；平面天线阵方向图计算中的仿射坐标FFT方法</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；硬件测试、仿真建模、实验平台辅助；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>通信/信号处理；电磁/微波；遥感/雷达；硬件/嵌入式；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/liuminggang/</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>data\raw_html\刘明罡_93e94083d8.html</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>data\raw_text\刘明罡_93e94083d8.txt</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>苏金龙</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>硕士生导师</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>暂无内容；团队成员；暂无内容；同专业硕导；总访问量；今日访问量；月访问量；地址：湖北省武汉市洪山区珞喻路1037号 邮政编码：430074</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>成果</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/sujinlong1/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>data\raw_html\苏金龙_642b5f5f1e.html</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>data\raw_text\苏金龙_642b5f5f1e.txt</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>邱才明</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>eicbd@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>邱才明教授，IEEE Fellow，国家重大人才工程A类，华中科技大学电子信息与通信学院院长。回国前任美国田纳西理工大学终身教授，曾担任贝尔实验室研究员，上海交通大学讲席教授，上海交通大学大数据工程技术研究中心主任等职务。；邱才明教授在无线通信领域有超过20年的国际经验，领导参加过多个重量级的通信领域的研究和开发项目。理论研究方面，邱才明教授因为UWB（超宽带通信）领域开创性工作为人所知，UWB被广泛用于雷达和分布式感知。邱才明教授对UWB信道多径脉冲失真畸变所建模型取代了50年代提出的经典Truin模型，并被IEEE802.15.4标准采纳。Andreas F. Molisch教授在其经典教科书《Wireless；Communications》中引用并介绍了邱才明教授的工作。此外，邱才明教授观察到波动方程具有时间翻转不变性和空间翻转不变性的数学事实，提出并系统性验证了时间翻转现象。邱才明教授曾领导开发了多个重量级的验证系统，其</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>下一代无线通信基础理论与系统，高维统计理论与应用，大数据与人工智能，深度学习理论与应用。</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ICC是通信领域最重要的会议之一</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>AI/机器学习；通信/信号处理；遥感/雷达</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>深度学习；人工智能</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>偏智能算法或机器学习应用方向，需要人工核验是否是真正的 AI/CV 课题。</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/qiucaiming/</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>data\raw_html\邱才明_7131bd1b9c.html</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>data\raw_text\邱才明_7131bd1b9c.txt</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>葛晓虎</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>xhge@mail.hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>华中科技大学电子信息与通信学院副院长，国家绿色通信与网络联合研究中心主任，二级教授，博士生导师，国家高层次人才特殊支持计划科技创新领军人才，中国科协海智计划特聘专家，爱思唯尔高被引学者，华中卓越学者特聘教授，澳大利亚悉尼科技大学兼职教授，华中科技大学—悉尼科技大学移动通信联合研究中心主任。</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>多篇代表性被评为IEEE通信学会领域最佳；国家科技部和国家自然基金委会评专家；中国通信学会会士；主持研究项目；国家自然科学基金重点国际合作项目；面向移动通信与计算融通的信息与能量耦合机理研究；国家自然科学基金重点项目</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>通信/信号处理；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/gexiaohu/index.html</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>data\raw_html\葛晓虎_d517989935.html</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>data\raw_text\葛晓虎_d517989935.txt</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>刘应状</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>liuyz@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>姓名；刘应状；性别；男；籍贯；湖北咸丰；出生年月日；相片；专业职称；教授；导师代码；1421；导师类别；博士生导师；学术兼职；欧洲核子中心CERN/LHC/ALICE合作组中国组技术协调人；兼职导师</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>博导；08100106 无线通信技术与系统；硕导研究方向；08100001 无线通信技术与系统；主要业绩</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>主持国家自然科学基金重点项目；无线网络干扰管理与容量研究；主持国家自然科学基金面上项目；主持科技部国际合作项目；下一代绿色无线网络联合研究；主持企业合作项目；主持重大国际合作项目；PHOS探测器FEE前端电子学系统研究；主要论文</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>通信/信号处理；遥感/雷达；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/liuyingzhuang/index.htm</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>data\raw_html\刘应状_bc538b70e5.html</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>data\raw_text\刘应状_bc538b70e5.txt</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>屈代明</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>qudaiming@163.com</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>基于大规模多天线阵列的免授权随机接入技术；基于大规模多天线阵列的免授权随机接入；OFDM多载波通信信号的幅度起落很大；减少信号的带内失真和带外干扰；又具有抑制信号PAPR的能力；导致通信系统频谱利用率明显降低；部分论文</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；硬件测试、仿真建模、实验平台辅助；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>通信/信号处理；电磁/微波</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>机器学习；人工智能；detection</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/qudaiming/index.html</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>data\raw_html\屈代明_47568e80e3.html</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>data\raw_text\屈代明_47568e80e3.txt</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>董燕</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>dongyan@mail.hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>现任华中科技大学电子信息与通信学院教授；获信号与信息处理专业工学硕士学位；在无线通信系统；卫星通信网络；无线传感器网络等领域；近年来承担了包括国家自然科学基金重大研究计划；重点项目；十三五航天系统；装备预研教育部联合基金；担任国家自然科学基金委</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>通信/信号处理；硬件/嵌入式；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>机器学习；深度学习</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/dongyan/index.htm</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>data\raw_html\董燕_3de3524627.html</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>data\raw_text\董燕_3de3524627.txt</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>王巍</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>教授研究员</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>当前主页抓取失败，无法判断方向。</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>https://faculty.hust.edu.cn/wei/zh_CN/index/750969/list/index.htm</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>data\raw_html\王巍_c49e77e0fe.html</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>data\raw_text\王巍_c49e77e0fe.txt</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>请求或解析失败：&lt;urlopen error _ssl.c:1063: The handshake operation timed out&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>肖泳</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>期刊论文</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>下一代网络技术；通信网络博弈论；低碳网络智能；机器学习与人工智能；无线通信网络；边缘智能；传感器网络与物联网；超低延迟通信技术等</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>AI/机器学习；通信/信号处理；硬件/嵌入式；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>机器学习；人工智能；detection；vision；machine learning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>偏智能算法或机器学习应用方向，需要人工核验是否是真正的 AI/CV 课题。</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/xiaoyong/index.html</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>data\raw_html\肖泳_542fb32e8b.html</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>data\raw_text\肖泳_542fb32e8b.txt</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>尹海帆</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>教授/研究员</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/yin</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>data\raw_html\尹海帆_a602d8aae1.html</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>data\raw_text\尹海帆_a602d8aae1.txt</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>王德胜</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>教授/研究员</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/wangdesheng/</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>data\raw_html\王德胜_96fd4b905a.html</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>data\raw_text\王德胜_96fd4b905a.txt</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>页面可读取文本较少，建议人工打开原始HTML或来源URL核验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>韩涛</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>韩涛，男，现任华中科技大学电子信息与通信学院教授，国家“绿色通信与网络国际联合研究中心”副主任。 1990年于华中理工大学获信息工程专业工学学士学位，1993年于华中理工大学获通信与电子系统工学硕士学位，2001年于华中科技大学获信息与通信工程工学博士学位。 1993年至今任职于华中科技大学，其中2010年至2011年，于美国佛罗里达大学做访问学者，任职客座副教授，2016年于澳大利亚悉尼科技大学任访问教授。为移动通信、计算机网络以及多媒体通信。在重要期刊和会议共发表文章80多篇。曾担任EAI Endorsed Transactions on Cognitive Communications期刊编辑，担任多个本领域顶级期刊的审稿人，担任多个国际学术会议程序委员会成员。多年来主持和参与了多项通信、多媒体等方面的科研项目，因作为核心人员参与“建筑设计方案计算机辅助评审系统”项目，1997年获得湖北省科技进步二等奖。；Short Bi</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>现任华中科技大学电子信息与通信学院教授；绿色通信与网络国际联合研究中心；主要研究方向为移动通信；计算机网络以及多媒体通信；多年来主持和参与了多项通信；建筑设计方案计算机辅助评审系统</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>CV/图像处理；AI/机器学习；通信/信号处理；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>偏视觉/图像与智能算法交叉，可重点看是否有检测、识别、分割、多模态或深度学习课题。</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/hantao</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>data\raw_html\韩涛_ea2abc2903.html</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>data\raw_text\韩涛_ea2abc2903.txt</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>彭薇</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>MORE+</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>/ 社会兼职；暂无内容；暂无内容；常用链接；1.华中科技大学</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>成果</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>人工智能；智能感知</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/pengwei1/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>data\raw_html\彭薇_7d2a18136c.html</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>data\raw_text\彭薇_7d2a18136c.txt</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>李强</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>qli_patrick@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>李强，2007年大学本科毕业于电子科技大学通信与信息工程学院。2011年博士研究生毕业于新加坡南洋理工大学电气与电子工程学院。2011年至2013年，于新加坡南洋理工大学任博士后研究员(Research Fellow)。2015年3月至6月，任英国谢菲尔德大学访问学者。2013年2月加入华中科技大学电子信息与通信学院，任副教授，2020年11月任教授，入选湖北省“楚天学者（楚天学子）”，入选华中科技大学“华中卓越学者（辰星岗）”。涉及无线协作通信、全双工中继、认知无线电/协作频谱共享、无线信息能量同传、软件定义网络、物联网、雾计算、网络边缘缓存等下一代移动通信热点研究领域，在IEEE Journal on Selected Areas in Communications， IEEE Transactions on Wireless Communications，IEEE Wireless Communications Magaz</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2013年2月加入华中科技大学电子信息与通信学院；主要研究方向涉及无线协作通信；软件定义网络；网络边缘缓存等下一代移动通信热点研究领域；作为负责人承担了国家重点研发计划项目课题；国家自然科学基金重点项目课题；国家自然科学基金青年基金项目；国家自然科学基金面上基金项目；参与了欧盟FP7项目；欧盟Horizon2020项目</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>欢迎有志于从事科学研究的同学报考研究生，也欢迎本科同学来交流学习。；Qiang Li received the B.Eng. degree in communication engineering from the University of Electronic Science and Technology of C</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>通信/信号处理；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>深度学习；人工智能；deep learning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/liqiang/</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>data\raw_html\李强_e180f0fd10.html</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>data\raw_text\李强_e180f0fd10.txt</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>万凯</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>教授/研究员</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>machine learning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/wankai/</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>data\raw_html\万凯_5f60560da7.html</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>data\raw_text\万凯_5f60560da7.txt</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>曹洋</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ycao@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Research Interest；• 虚拟/增强现实内容的云-边协同高清传输；在中兴、中国移动和腾讯等知名企业的支持下，为解决无线网络下大规模视频及VR/AR视频传输的难题，本课题组首创从基于弱监督学习的无线网络模态分类问题出发，把握复杂多变的无线网络的内在特征；结合前沿的云计算-边缘计算协同技术和自适应码率传输技术，从多维资源优化方法及深度增强学习两个方向展开深入研究，有效提升了在有限网络条件下观看视频的用户体验质量。在设备方面，课题组提供高性能GPU服务器，实验网络，VR头戴式显示器及GoPro全景摄像头等。；• 面向物联网的分布式/边缘协同计算；随着物联网时代到来以及终端数据量的指数级增加，数据中心算力逐渐不足以支撑海量数据处理任务。在多项国家级项目的支持下，课题组提出边缘侧多节点集群，结合计算虚拟化技术，构建分布式计算系统，结合凸优化理论及深度增强学习方法展开任务卸载和调度算法研究，以缓和云端计算压力并提升用户服务体验</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>主持国家级以及企业预研项目多项；基于网络；计算与智能技术打破数字与现实的边界</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>为解决无线网络下大规模视频及VR；AR视频传输的难题；本首创从基于弱监督学习的无线网络模态分类问题出发；把握复杂多变的无线网络的内在特征；有效提升了在有限网络条件下观看视频的用户体验质量；实验网络；在多项国家级项目的支持下；构建分布式计算系统；以验证算法有效性和k8s；在国家级项目和高新企业的支持下</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>CV/图像处理；通信/信号处理；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>视频处理；深度学习；detection；video；vision</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>偏图像、视频、视觉感知或成像处理方向，适合从论文复现和数据处理切入。</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/caoyang/</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>data\raw_html\曹洋_6a779ec4ef.html</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>data\raw_text\曹洋_6a779ec4ef.txt</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>周桂</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>博导</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Personal profile；周桂，华中科技大学电子信息与通信学院教授，博士生导师，国家级青年人才（海外）。2015及2019年在北京理工大学分别获得学士和硕士学位，2022年在英国伦敦玛丽女王大学（Queen Mary University of London, QMUL）获得博士学位，2022年获洪堡学者奖学金赴德国埃尔朗根-纽伦堡大学（FAU Erlangen-Nürnberg）从事博士后研究。研究领域为无线通信中的信号处理，包括传输设计，信道估计与定位，通感一体化，AI辅助通信等。近年来在IE...；More+</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Research focus；暂无内容；团队成员；Research group；暂无内容；地址：湖北省武汉市洪山区珞喻路1037号 邮政编码：430074；访问量；|；手机版</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>· 成果</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>AI/机器学习；通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>偏智能算法或机器学习应用方向，需要人工核验是否是真正的 AI/CV 课题。</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/~rQZfM3/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>data\raw_html\周桂_0c0f2971f5.html</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>data\raw_text\周桂_0c0f2971f5.txt</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>王琛</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>副研究员</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>硕导</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>社会兼职/；查看更多；查看更多</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>成果</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>模式识别</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/chenwang/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>data\raw_html\王琛_3724aef4bc.html</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>data\raw_text\王琛_3724aef4bc.txt</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>徐争光</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>xray@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>徐争光，男，博士，华中科技大学电子信息与通信学院副教授。2004年本科毕业于华中科技大学电信系提高班，2006年和2009年获得华中科技大学硕士和博士学位，毕业后留校工作。主持国家自然科学基金、国家科技支撑计划等课题，国内外期刊会议发表论文30余篇。包括软件无线电、通信信号分析。；个人网站；无；个人邮箱；xray@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>华中科技大学电子信息与通信学院副教授；主持国家自然科学基金；通信信号分析；代表性论文</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/xuzhengguang/</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>data\raw_html\徐争光_cd04b60dd2.html</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>data\raw_text\徐争光_cd04b60dd2.txt</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>黄本雄</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>姓名；黄本雄；性别；男；籍贯；湖北省；出生年月日；1966.7；相片；专业职称；教授；导师代码；215；导师类别；博士生导师；学术兼职；兼职导师</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>博导；2011年 08100103 空间通信技术与系统；2011年 08100104 空间信息获取与处理；2011年 08100106 无线通信技术与系统；2011年 08100107 现代网络技术；2011年 08100108 现代信号处理；2011年 08100109 信息安全；硕导研究方向；2011年 08100101 无线通信技术与系统；2011年 08100102 现代信号处理；2011年 08100103 现代网络技术；2011年 08100105 信息安全；2011年 08100107 空间信息获取与处理；2011年 08100108 空间通信技术与系统；2011年 08100203 现代信号处理；主要业绩；主要著作；1、著作名称：通信原理，出版时间：2006-05-01，出版社名称：清华大学出版社，本人署名次序2</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>主要论文</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；安全论文阅读、实验复现、工具链整理；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>通信/信号处理；网络/物联网；信息安全</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/huangbenxiong/</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>data\raw_html\黄本雄_b58b6d5611.html</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>data\raw_text\黄本雄_b58b6d5611.txt</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>吴伟民</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>wuwm@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1. 无线通信系统与样机研发；2. 4G/5G的L2协议创新性研究；3. WiFi协议创新性研究，MAC传输优；4. 异构融合组网；通信方式；邮箱：wuwm@hust.edu.cn；已完成的项目；1. 承担完成的国家项目；a. 863计划子课题；（1）深空信道模型、中继网络架构和通信传输协议，2012年，牵头单位北京理工大学；（2）5G 高通量无线网络架构与关键技术研发，2014年，牵头单位华为技术有限公司；b. 民口重大专项子课题；（3）IMT-Advanced新型无线传输技术研发，2009年，牵头单位清华大学；（4）基于TD-LTE公网集群业务系统研发与验证，2013年，牵头单位华为技术有限公司；（5）面向LTE-Advanced的终端软基带技术，2013年，牵头单位中科院微电子所；c. 支撑计划子课题；（6）面向；IMT-Advanced标 准化无线接口关键技术研究，2008年，牵头单位清华大学；d. 教育部-中国移动科研</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>发表；(1) Xiaoqing Peng, Weimin Wu, Jun Sun, Yingzhuang Liu. Sparsity-Boosted Detection for Large MIMO Systems. IEEE Communications Letters, 2015.2.6, 19(2): 191~1</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>CV/图像处理；通信/信号处理；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>detection；video；vision</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>偏图像、视频、视觉感知或成像处理方向，适合从论文复现和数据处理切入。</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/wuweimin/</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>data\raw_html\吴伟民_8d7ae772b0.html</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>data\raw_text\吴伟民_8d7ae772b0.txt</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>王非</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>wangfei@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>华中科技大学电子信息与通信学院副教授；多年来一直从事通信与信息系统；主持和参与2项国家自然科学基金项目；参与了多项国家重大项目；新一代宽带无线移动通信网；国内优势科研机构和通信企业的联合科研工作</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>深度学习；recognition</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/wangfei/</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>data\raw_html\王非_59d1d7fcf1.html</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>data\raw_text\王非_59d1d7fcf1.txt</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>戴彬</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>daibin@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>戴彬，男，博士，华中科技大学电子与信息工程系副教授。2016年-2017年在纽约大学Tandon学院访问交流。2007年-2009年在香港城市大学计算机科学系任高级副研究员、研究员。2006年博士毕业于华中科技大学电信系，2002年获得华中科技大学电信息系硕士学位，2000年本科毕业于华中科技大学电信系提高班。主持国家自然科学基金项目、国家科技支撑计划项目、国家重大科研专项、校企合作项目多项。已发表会议与期刊论文40篇多篇，专利授权10多项。目前的包括下一代网络技术、5G核心网、智能路由规划、智能网络运维等。曾多次担任国际重要会议的组委会成员和评审专家，国家自然科学基金评审专家，省自然科学基金评审专家，以及国际权威期刊评审专家，ISO/TC164/SC6国际标准化工作组专家成员，CCSA；TC614-网络5.0技术标准推进委员会成员。；个人网站；http://xxxxxx；个人邮箱；daibin@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>主持国家自然科学基金项目；国家科技支撑计划项目；校企合作项目多项；目前的主要研究方向包括下一代网络技术；智能网络运维等；国家自然科学基金评审专家；省自然科学基金评审专家；代表性论文</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>AI/机器学习；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>偏智能算法或机器学习应用方向，需要人工核验是否是真正的 AI/CV 课题。</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/daibin/</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>data\raw_html\戴彬_a91ab288f1.html</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>data\raw_text\戴彬_a91ab288f1.txt</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>黑晓军</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>计算机与信息科学系从事对等网络；现为电子信息与通信学院副教授；计算机网络；网络系统设计与实验；智能网络计算；科研项目；国家自然科学基金项目；大用户量异构软件定义网络关键技术研究</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>通信/信号处理；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>机器学习</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/heixiaojun/</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>data\raw_html\黑晓军_286cc78cfd.html</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>data\raw_text\黑晓军_286cc78cfd.txt</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>唐祖平</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>tang_zuping@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>唐祖平，博士，华中科技大学电子信息与通信学院副教授。为导航/通信信号设计、信号处理。他是北斗全球系统信号设计团队的核心成员之一，主要从事信号调制、复用及扩频码设计与优化工作；是中欧、中美、中俄卫星导航系统双边协调技术工作组成员，为北斗与Galileo、GPS、Glonass系统的兼容与互操作做出了重要贡献。主持和参与自然科学基金、重大专项、重点研发计划等项目10余项，在国内外期刊和会议发表论文40余篇，获得美国、欧洲、日本、中国等专利授权10余项，获教育部科技进步二等奖1项、军队科技进步二等奖1项。；承担课程；l 电子线路设计、测试与实验；l 卫星通信原理；l 卫星通信系统；l 空间通信系统设计与实验</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>华中科技大学电子信息与通信学院副教授；通信信号设计；他是北斗全球系统信号设计团队的核心成员之一；主要从事信号调制；中俄卫星导航系统双边协调技术工作组成员；Glonass系统的兼容与互操作做出了重要贡献；主持和参与自然科学基金；重点研发计划等项目10余项；卫星通信原理；卫星通信系统</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>目标检测；vision</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/tangzuping/</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>data\raw_html\唐祖平_b0d0575831.html</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>data\raw_text\唐祖平_b0d0575831.txt</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>胡梦兰</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>副教授副研究员</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>humenglan@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Research Interests；Mobile Cloud &amp; Edge Computing；云与边缘计算；Internet of Things；物联网；Mobile Computing；移动计算；Distributed Computing；分布式计算；Wireless Network；无线网络；Unmanned Aerial Vehicle；无人机</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>通信/信号处理；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>video；vision</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/humenglan/humenglan.html</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>data\raw_html\胡梦兰_c64c22b11d.html</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>data\raw_text\胡梦兰_c64c22b11d.txt</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>鲁放</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>副教授副研究员</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/lufang/</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>data\raw_html\鲁放_af08c5a0f0.html</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>data\raw_text\鲁放_af08c5a0f0.txt</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>页面可读取文本较少，建议人工打开原始HTML或来源URL核验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>谭力</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>硕导</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Personal profile</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Research focus；未来无线通信系统物理层关键技术与系统验证、通信信号处理、绿色通信与能效评价、SoC设计方法建模与概率性逻辑电路建模与分析；团队成员；Research group；暂无内容；地址：湖北省武汉市洪山区珞喻路1037号 邮政编码：430074；访问量；|；手机版</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>· 成果</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；硬件测试、仿真建模、实验平台辅助；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>通信/信号处理；硬件/嵌入式</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/tanli1/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>data\raw_html\谭力_e6b06789b1.html</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>data\raw_text\谭力_e6b06789b1.txt</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>高雅玙</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>yayugao@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Research Interests；Distributed Multiple Access；分布式多址接入；Next-Generation Wireless Networks；6G &amp; 未来WiFi；Network Intelligence；网络智能；AI+；AI赋能垂直领域；Research Fundings 研究项目；Ongoing 在研；Enterprise Cooperation Project with Huawei, Principal Investigator, 2023.1-.；Enterprise Cooperation Project with State Grid Corporation of China Nanrui III, Principal Investigator, 2023.1-.；Enterprise Cooperation Project with State Grid Corporati</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>期刊论文</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>AI/机器学习；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>detection；deep learning；machine learning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>偏智能算法或机器学习应用方向，需要人工核验是否是真正的 AI/CV 课题。</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/gaoyayu/</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>data\raw_html\高雅玙_84761e3509.html</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>data\raw_text\高雅玙_84761e3509.txt</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>廖振宇</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>副教授副研究员</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>通信工程系</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>image；vision；machine learning</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/liaozhenyu/</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>data\raw_html\廖振宇_ef2d3d03bb.html</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>data\raw_text\廖振宇_ef2d3d03bb.txt</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>钟祎</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>博导</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Personal profile</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Research focus；时空无线网络建模与优化；绿色低碳通信与6G网络技术；新一代无线接入与协议创新；团队成员；Research group；· 团队名称：国家绿色通信与网络国际联合研究中心</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>· 成果</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>依托华中科技大学电子信息与通信学院开展建设</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>通信/信号处理；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/zhongyi/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>data\raw_html\钟祎_a7a19836cc.html</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>data\raw_text\钟祎_a7a19836cc.txt</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>陈达</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Personal Profile</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>陈达，副教授、博士生导师。为无线通信中的多载波调制、波形设计和信号处理。主持国家自然科学基金3项，国家自然科学基金重点项目子课题1项，国家重点研发计划子课题1项，出版学术专著2部，在国内外通信领域学术期刊及会议上发表学术论文60余篇，申请国家发明专利23项，已授权17项。担任中国通信（China Communications）、Digital Communications and Networks等4个SCI期刊编委/客座编委，2023年入选中国电子学会通信分会首届青年委员，获2017、2020和2021年度最佳编委奖，获2021年度中国电子学会科技进步一等奖，2022年度湖北省自然科学二等奖。</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>成果</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/chenda/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>data\raw_html\陈达_0d4cc7b551.html</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>data\raw_text\陈达_0d4cc7b551.txt</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>叶俊良</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>中文主页；个人简介；个人简介；于2018年获得华中科技大学信息与通信工程博士学位，师从葛晓虎教授，2018年至2022年任美国国家标准与技术研究院 （National Institute of Standards and Technology, U.S. Department of Commerce，简称NIST）国际副研究员（International Associate Researcher），合作者为Hamid Gharavi博士（IEEE Life Fellow，IEEE Wireless Communications前主编，美国政府资深科学家），并于2023年11月加盟华中科技大学电子信息与通信学院，并于2024年获批中组部海外引才专项计划（最高资助）。</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>· 成果</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>人工智能</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/YeJunliang/zh_CN/more/2538182/jsjjgd/index.htm</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>data\raw_html\叶俊良_0be08597fe.html</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>data\raw_text\叶俊良_0be08597fe.txt</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>程文青</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>chengwq@mail.hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>姓名；程文青；性别；女；籍贯；出生年月日；相片；专业职称；教授；导师代码；85；导师类别；博士生导师；学术兼职；兼职导师</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>博导；2011年 08100101 多媒体通信与信息处理；2011年 08100106 无线通信技术与系统；2011年 08100107 现代网络技术；硕导研究方向；2011年 08100101 无线通信技术与系统；2011年 08100103 现代网络技术；2011年 08100104 多媒体通信与信息处理；2012年 08100003 现代网络技术；2012年 08100005 信息安全；2012年 08100009 生物信息处理；主要业绩；主要著作</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>主要研究领域包括无线传感器网络；高速网络通信技术；作为课题负责人主持国家自然科学基金项目；可重构MIMO的无线传感器网络信息处理与传输；863计划项目；教育部科技项目；教育部科技项目专家库与网上项目管理平台；参与国家自然科学基金项目2项；863计划项目1项；无线传感器网络</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>国家攻关项目；资源分布式管理算法与系统设计；可重构MIMO的无线传感器网络信息处理与传输；国家自然科学基金；无线传感网络可重构MIMO算法设计；支持多通信平台的RFID中间件技术的研究与开发；国家863计划项目；RFID中间件系统设计；基于网络效用最大化的无线传感器网络研究；基于网络效用最大化的跨层优化算法设计</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；安全论文阅读、实验复现、工具链整理</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>CV/图像处理；通信/信号处理；硬件/嵌入式；网络/物联网；信息安全</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>偏图像、视频、视觉感知或成像处理方向，适合从论文复现和数据处理切入。</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/chengwenqing/</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>data\raw_html\程文青_b7993c31ff.html</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>data\raw_text\程文青_b7993c31ff.txt</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>刘文予</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>liuwy@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>人工智能、机器学习、计算机视觉、机器人等；主讲课程；“数据结构”；本科生；“软件课程设计”；本科生；“视觉计算”；博士生</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>主持完成8项国家自然科学基金；正在承担国家自然科学基金重点项目；国家重点研发计划等纵向项目；平安保险等横向项目；近几年代表性期刊论文；SCI期刊论文</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>CV/图像处理；AI/机器学习</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>计算机视觉；视频处理；模式识别；机器学习；人工智能；detection；segmentation；recognition；image；video；visual；vision</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>偏视觉/图像与智能算法交叉，可重点看是否有检测、识别、分割、多模态或深度学习课题。</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/liuwenyu/</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>data\raw_html\刘文予_fc33b2bd14.html</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>data\raw_text\刘文予_fc33b2bd14.txt</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>喻莉</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>教授/研究员</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>recognition；image；video</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/yuli/</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>data\raw_html\喻莉_37c1ee1381.html</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>data\raw_text\喻莉_37c1ee1381.txt</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>田岩</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>人工智能和大数据等方面的研究工作；作为项目负责人和主要成员先后主持或参与国家；国家自然科学基金；省部级课题及其多家企事业单位的合作项目</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>AI/机器学习</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>图像处理；人工智能</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>偏智能算法或机器学习应用方向，需要人工核验是否是真正的 AI/CV 课题。</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/tianyan/</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>data\raw_html\田岩_c586741230.html</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>data\raw_text\田岩_c586741230.txt</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>王邦</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>博导</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Personal profile；Dr. Bang Wang obtained his B.E. and M.S. from the Department of Electronics and Information Engineering of Huazhong University of Science and Technology (HUST) Wuhan, China in 1996 and 2000, respectively, and his PhD degree in Electrical and Computer Engineering (ECE) Department of National University of Singapore (NUS) Singapore in 2004. He is now working as a professor in the School of Electr...；Mo</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Research focus；暂无内容；团队成员；Research group；暂无内容；地址：湖北省武汉市洪山区珞喻路1037号 邮政编码：430074；访问量；|；手机版</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>· 成果</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>AI/机器学习；通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>偏智能算法或机器学习应用方向，需要人工核验是否是真正的 AI/CV 课题。</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/wangbang/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>data\raw_html\王邦_97294bb022.html</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>data\raw_text\王邦_97294bb022.txt</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>彭凯</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>教授/研究员</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>pkhust@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Research Interests；Edge Computing；边缘计算；Artificial Intelligence；人工智能；Cloud Computing；云计算；Blockchain Technology；区块链；Network Security；网络安全</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>主要项目</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；安全论文阅读、实验复现、工具链整理</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>AI/机器学习；网络/物联网；信息安全</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>机器学习；人工智能；machine learning</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>偏智能算法或机器学习应用方向，需要人工核验是否是真正的 AI/CV 课题。</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/pengkai/pengkai.html</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>data\raw_html\彭凯_331a9acf82.html</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>data\raw_text\彭凯_331a9acf82.txt</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>朱明</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>zhuming@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>朱明，男，博士，华中科技大学电子信息与通信学院教授。2008年获得华中科技大学信息与通信工程博士学位，师从王殊教授。2001年本科毕业于华中科技大学，2004年获得华中科技大学通信与信息系统硕士学位。于2014年至2015年，在美国西北大学机械工程系做访问学者，师从Richard；M.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lueptow教授（McCormick工程和应用学院的资深副院长、产品设计和开发管理硕士项目联合创始人）。目前主持国家自然科学基金项目两项，国家重点研发项目一项。已发表顶级国际会议与杂志论文12篇。目前的包括超声信号处理、声学气体检测、火灾信号处理、嵌入式和DSP系统设计等。；个人网站；http://itec.hust.edu.cn/~zhuming；个人邮箱；zhuming@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>产品设计和开发管理硕士项目联合创始人；目前主持国家自然科学基金项目两项；国家重点研发项目一项；目前的主要研究方向包括超声信号处理；火灾信号处理；嵌入式和DSP系统设计等；代表性论文</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>通信/信号处理；硬件/嵌入式</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>detection；video</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/zhuming</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>data\raw_html\朱明_cc4ee1c6d3.html</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>data\raw_text\朱明_cc4ee1c6d3.txt</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>刘威</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>教授研究员</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>待人工核验</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>当前主页抓取失败，无法判断方向。</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>https://faculty.hust.edu.cn/wliu/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>data\raw_html\刘威_da273f9df8.html</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>data\raw_text\刘威_da273f9df8.txt</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>请求或解析失败：&lt;urlopen error _ssl.c:1063: The handshake operation timed out&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>郭鹏</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>教授/研究员</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>智能感知与计算；团队成员；暂无内容；同专业博导；同专业硕导；总访问量；今日访问量；月访问量；地址：湖北省武汉市洪山区珞喻路1037号 邮政编码：430074</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>工程系统</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>AI/机器学习；通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>智能感知</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>偏智能算法或机器学习应用方向，需要人工核验是否是真正的 AI/CV 课题。</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/guopeng/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>data\raw_html\郭鹏_333f432e36.html</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>data\raw_text\郭鹏_333f432e36.txt</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>杨欣</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>xinyang2014@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>主要从事计算机视觉和医学影像智能分析领域研究工作；代表性论文</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>CV/图像处理</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>计算机视觉；segmentation；recognition；image；video；vision</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>偏图像、视频、视觉感知或成像处理方向，适合从论文复现和数据处理切入。</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/yangxin/</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>data\raw_html\杨欣_68534739ff.html</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>data\raw_text\杨欣_68534739ff.txt</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>杨铀</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>教授/研究员</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>主要从事以视觉感知与计算为核心的计算机视觉；立体视频系统等方面的研究工作；数字化感知方法与装备；灾害数字化感知与重建；应急救援感知与通信装备；智慧城市与城市安全；多模态心脏影像数据处理与智能诊断；多视点多光谱感知与计算；元宇宙视频系统与6DoF交互式视频系统；行为意图与人机交互系统</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；安全论文阅读、实验复现、工具链整理</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>CV/图像处理；AI/机器学习；通信/信号处理；光电/激光；信息安全</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>计算机视觉；图像处理；视频处理；人工智能；图像分割；点云；多模态；detection；segmentation；recognition；image；video；visual；vision；deep learning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>偏视觉/图像与智能算法交叉，可重点看是否有检测、识别、分割、多模态或深度学习课题。</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/yangyou/</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>data\raw_html\杨铀_72de3b2d8a.html</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>data\raw_text\杨铀_72de3b2d8a.txt</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>刘琼</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>教授/研究员</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>q.liu@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>detection；image；video；visual；vision</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/professor/liuqiong/</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>data\raw_html\刘琼_f3faee0e20.html</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>data\raw_text\刘琼_f3faee0e20.txt</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>王兴刚</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Personal Profile；王兴刚，华中科技大学电信学院教授博导，国家“万人计划”青年拔尖人才，现任Image and Vision Computing期刊（Elsevier, IF 4.2）共同主编。分别于2009年和2014年在华中科技大学获得了本科和博士学位，期间在美国UCLA和天普大学访问研究。</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Research Focus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>成果</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>CV/图像处理</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>计算机视觉；模式识别；深度学习；人工智能；目标检测；多模态；recognition；image；vision</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>偏图像、视频、视觉感知或成像处理方向，适合从论文复现和数据处理切入。</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/xwang/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>data\raw_html\王兴刚_ce79d9cf25.html</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>data\raw_text\王兴刚_ce79d9cf25.txt</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>程起敏</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>chengqm@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>发表(近5年)；Cheng Q* , Zhang Q , Fu P , et；al. A survey and analysis on automatic image annotation[J]. Pattern；Recognition, 79(2018):242-259. DOI: 10.1016/j.patcog.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>CV/图像处理</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>计算机视觉；图像处理；深度学习；遥感图像处理；detection；recognition；image；deep learning</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>偏图像、视频、视觉感知或成像处理方向，适合从论文复现和数据处理切入。</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/chengqimin/</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>data\raw_html\程起敏_5aaaa4e184.html</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>data\raw_text\程起敏_5aaaa4e184.txt</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>冯镔</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>博士生导师</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2006年毕业于华中科技大学电子与信息工程系，获信息与通信工程一级学科博士学位；2009年-2010年赴香港科技大学访问交流。目前是人体动作行为分析，包括手势识别、声纹识别、步态识别等。先后主持国家自然科学基金，湖北省自然科学基金，以及多项横向合作课题。已发表论文30多篇，包括TIP，CSVT，Pattern Recognition，ICCV等国际顶级期刊和会议，获国内授权技术发明专利6项。担任TIP，CSVT，TMS，ICV等多个期刊的常邀审稿人。；查看更多&gt;</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>成果</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>CV/图像处理；通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>图像识别；多模态；recognition</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>偏图像、视频、视觉感知或成像处理方向，适合从论文复现和数据处理切入。</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/fengbin1/zh_CN/index/1489780/list/index.htm</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>data\raw_html\冯镔_a40389f56d.html</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>data\raw_text\冯镔_a40389f56d.txt</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>周瑜</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>博导</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Personal profile</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Research focus；计算机视觉，开放场景视觉感知，工业视觉；团队成员；Research group；暂无内容；地址：湖北省武汉市洪山区珞喻路1037号 邮政编码：430074；访问量；|；手机版</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>· 成果</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>CV/图像处理；通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>计算机视觉；人工智能</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>偏图像、视频、视觉感知或成像处理方向，适合从论文复现和数据处理切入。</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/yuzhou</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>data\raw_html\周瑜_de5d87e3bb.html</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>data\raw_text\周瑜_de5d87e3bb.txt</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>黄浩军</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>副教授副研究员</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>hjhuang@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>vision；deep learning</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/huanghaojun/index.html</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>data\raw_html\黄浩军_ddbe770cfe.html</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>data\raw_text\黄浩军_ddbe770cfe.txt</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>徐晶</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>xujing@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>反向散射通信关键技术研究；湖北省自然科学基金项目；国家自然科学基金项目；面向智能化教学环境的多情境数据感知技术</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>通信/信号处理；遥感/雷达</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>detection；video</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/xujing/</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>data\raw_html\徐晶_e41ed9c6c7.html</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>data\raw_text\徐晶_e41ed9c6c7.txt</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>杨鹏</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>副教授副研究员</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/yangpeng/index.html</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>data\raw_html\杨鹏_7b4e00e988.html</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>data\raw_text\杨鹏_7b4e00e988.txt</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>许毅平</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>副教授副研究员</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/xuyiping/</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>data\raw_html\许毅平_ee0617a5c5.html</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>data\raw_text\许毅平_ee0617a5c5.txt</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>页面可读取文本较少，建议人工打开原始HTML或来源URL核验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>徐端全</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>硕士生导师</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>xudq@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1；图像处理 视频编码 模式识别 嵌入式系统；2 主持项目；1. 防伪票据智能处理关键技术及设备研发(湖北省技术创新专项重大项目),2018-2020。；2. 食品安全电子溯源数据采集交换与标识关键技术研究与应用(国家科技支撑计划项目), 2015-2017。；3. 综合防伪关键技术研究及系统应用开发(国家支撑计划项目),2012-2015。；4. 基于复向量小波的病理显微图像纹理特征表示与提取(湖北省自然科学基金),2013-2014。；5. 制药企业RFID综合应用系统开发(湖北省科技支撑计划项目),2013-2014。；6. 医疗检测新技术与新产品开发(武汉康创科技有限公司),2011-2014。；7. 金融票据防伪与检测关键技术与应用合作研究(科技部国际合作项目),2011-2014。；8. 防伪鉴定与溯源关键技术研究(科技部支撑计划项目),2011-2014。</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>从事图像处理；嵌入式系统方面的研究工作；主持国家科技支撑计划项目；湖北省科技计划项目；湖北省自然科学基金项目以及企业合作研究等多个项目</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；安全论文阅读、实验复现、工具链整理；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>CV/图像处理；通信/信号处理；硬件/嵌入式；信息安全</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>图像处理；模式识别；segmentation；recognition；image；video</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>偏图像、视频、视觉感知或成像处理方向，适合从论文复现和数据处理切入。</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>http://eic.hust.edu.cn/aprofessor/xuduanquan/index.htm</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>data\raw_html\徐端全_ec2570c65e.html</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>data\raw_text\徐端全_ec2570c65e.txt</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>许炜</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>硕士生导师</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Personal Profile；许 炜；华中科技大学 电子信息与通信学院 | 教授</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>音乐智能：将人工智能技术深度应用于音乐教育领域，解决音乐技能的客观评价与智能辅助问题，实现自动转录、精准评分与个性化反馈。；课堂智能：通过多模态感知技术对课堂教学全过程量化分析，实现学生注意力评估、师生互动识别、教学行为编码，构建数据驱动的教学效能评价体系。；计算机视觉：研究视觉模型鲁棒性、生成与编辑，建立对抗鲁棒性基准，探索基于扩散模型的视觉内容编辑技术。；主持或参加的国家自然科学基金项目；国家自然科学基金面上项目，62277019，面向音乐教育的唱歌智能评价技术研究，2023-01-01 至 2026-12-31，在研，主持；国家自然科学基金面上项目，62277019，钢琴教学中智能辅助技术研究，2018-01-01 至 2022-12-31，结题，主持；国家自然科学基金国际(地区)合作与交流项目，62381260591，参加艺术与科技学术研讨会，2023-09-30 至 2023-12-31，结题，主持</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>成果</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>CV/图像处理；AI/机器学习；通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>计算机视觉；人工智能；目标检测；多模态；detection；recognition；image；visual；vision</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>偏视觉/图像与智能算法交叉，可重点看是否有检测、识别、分割、多模态或深度学习课题。</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/xuwei7/zh_CN/index/1711225/list/index.htm</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>data\raw_html\许炜_20ec034a20.html</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>data\raw_text\许炜_20ec034a20.txt</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>闫增强</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>副研究员</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>博导</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Personal profile</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>闫增强，华中科技大学电子信息与通信学院副研究员（教学科研并重岗），湖北省百人计划创新人才，武汉英才（优秀青年）。2020年于香港科技大学计算机科学与工程系获博士学位，2020-2021年于香港科技大学从事博士后研究工作，2021年12月加入华中科技大学电子信息与通信学院。为人工智能与医学图像处理，近年来以第一作者/通信作者在IEEE TMI、IEEE JBHI、AAAI、IJCAI、MICCAI等期刊会议累计发表论文20余篇，其中中科...；More+</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>· 成果；教学研究</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>长期专注人工智能；医学图像处理的研究；旨在研究轻量高效的医学图像处理算法</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>CV/图像处理；AI/机器学习；通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>图像处理；人工智能；医学图像</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>偏视觉/图像与智能算法交叉，可重点看是否有检测、识别、分割、多模态或深度学习课题。</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/yanzengqiang/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>data\raw_html\闫增强_dd3d812553.html</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>data\raw_text\闫增强_dd3d812553.txt</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>邓田</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>硕导</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Personal profile</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Research focus；嵌入式系统；微弱信号处理；光学颗粒物传感；团队成员；Research group；· 团队名称：消防与应急救援国家工程实验室</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>· 成果</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>本实验室分布于南一楼701、西319和西320三处，共有副教授1人，讲师1人，高级工程师1人，博士后1人，博士生5人，硕士生12人；地址：湖北省武汉市洪山区珞喻路1037号 邮政编码：430074；访问量；|；手机版</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>通信/信号处理；光电/激光；硬件/嵌入式</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>深度学习</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/dengtian2/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>data\raw_html\邓田_da2373561e.html</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>data\raw_text\邓田_da2373561e.txt</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>鲜可</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>硕士生导师</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>鲜可，华中科技大学电子信息与通信学院副教授，硕士生导师，入选国家海外引才专项（2024）、华中科技大学小米青年学者（2024）。本科和博士均毕业于华中科技大学人工智能与自动化学院，师从曹治国教授。16年8月至17年9月在澳大利亚阿德莱德大学沈春华教授团队访学，19年3月至19年6月受邀在美国Adobe研究院实习。21年10月至23年11月，在新加坡南洋理工大学从事博士后研究工作。是计算机视觉和计算摄影学，近年来研究兴趣主要包括鲁棒深度估计、景深渲染、图像视频3D生成和编辑、说话数字人、具身智能等。截至2025年12月，在计算机视觉相关领域已发表论文60余篇，其中以第一/通讯作者在TPAMI/IJCV以及CVPR/ICCV等本领域国际权威期刊和顶...；查看更多&gt;</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>成果</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>CV/图像处理；AI/机器学习；通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>计算机视觉；模式识别；人工智能；image；video；vision</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>偏视觉/图像与智能算法交叉，可重点看是否有检测、识别、分割、多模态或深度学习课题。</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/XianKe/zh_CN/index/2541862/list/index.htm</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>data\raw_html\鲜可_91badb9b43.html</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>data\raw_text\鲜可_91badb9b43.txt</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>刘高扬</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>博导</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>电子信息与通信学院</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>暂无内容；团队成员；暂无内容；同专业博导；总访问量；今日访问量；月访问量；地址：湖北省武汉市洪山区珞喻路1037号 邮政编码：430074</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>成果</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>通信/信号处理</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>人工智能；多模态；大模型</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/LiuGaoyang/zh_CN/index/2616394/list/index.htm</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>data\raw_html\刘高扬_e327d37bae.html</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>data\raw_text\刘高扬_e327d37bae.txt</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>吴科君</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>信息工程系</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>image；visual；vision；multimodal</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>http://faculty.hust.edu.cn/WuKejun</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>data\raw_html\吴科君_f4ca0c50f7.html</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>data\raw_text\吴科君_f4ca0c50f7.txt</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>汪小燕</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>硕士生导师</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>教学实验中心</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>姓名；汪小燕；性别；女；籍贯；出生年月日；相片；专业职称；教授；导师代码；631；导师类别；硕士生导师；学术兼职；兼职导师</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>硕导；2011年 08100101 无线通信技术与系统；2011年 08100102 现代信号处理；2011年 08100103 现代网络技术；2011年 08100203 现代信号处理；2012年 08100001 无线通信技术与系统；2012年 08100002 现代信号处理；2012年 08100003 现代网络技术；主要业绩；主要著作</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>国家攻关项目；理论与算法研究；基于无线网络的应急搜救关键技术研究；国家自然科学基金；主要论文；0的远程节能控制系统的设计与实现</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>通信/信号处理；网络/物联网</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>主要是通信或信号处理，若只出现泛化“智能处理”，AI/CV 相关性需人工核验。</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>http://ei.hust.edu.cn/professor/wangxiaoyan/</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/jxsyzx.htm</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>data\raw_html\汪小燕_12d64fb221.html</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>data\raw_text\汪小燕_12d64fb221.txt</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>邓天平</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>教学实验中心</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>其他/待核验</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>当前公开文本不足以判断，建议打开主页和原始文本人工核验。</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>http://ei.hust.edu.cn/professor/dengtianping/</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>https://eic.hust.edu.cn/xygk/szdw/jxsyzx.htm</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>data\raw_html\邓天平_a5cdced3d2.html</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>data\raw_text\邓天平_a5cdced3d2.txt</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>页面可读取文本较少，建议人工打开原始HTML或来源URL核验。</t>
         </is>
       </c>
     </row>

--- a/output/teachers.xlsx
+++ b/output/teachers.xlsx
@@ -93,30 +93,50 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>undergrad_openness</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>publication_potential</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>interest_match</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>fit_summary</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>来源URL</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>发现来源URL</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>原始HTML路径</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>原始文本路径</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>抓取状态</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -205,30 +225,50 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>主页抓取失败，三个维度均需人工核验。</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>https://faculty.hust.edu.cn/hufei/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>data\raw_html\胡飞_5c59fb2916.html</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>data\raw_text\胡飞_5c59fb2916.txt</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>请求或解析失败：&lt;urlopen error _ssl.c:1063: The handshake operation timed out&gt;</t>
         </is>
@@ -282,7 +322,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析</t>
+          <t>基于公开方向推测：处理遥感/雷达成像数据，复现实验中的滤波、检测或目标识别模块；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -307,7 +347,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -317,30 +357,50 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/liqingxia/</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>data\raw_html\李青侠_1757adb48b.html</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>data\raw_text\李青侠_1757adb48b.txt</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -394,7 +454,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；硬件测试、仿真建模、实验平台辅助</t>
+          <t>基于公开方向推测：处理遥感/雷达成像数据，复现实验中的滤波、检测或目标识别模块；复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -409,7 +469,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t/>
+          <t>数据挖掘</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -419,7 +479,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -429,30 +489,50 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/mahong/</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>data\raw_html\马洪_3d1a91e8a5.html</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>data\raw_text\马洪_3d1a91e8a5.txt</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -506,7 +586,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；硬件测试、仿真建模、实验平台辅助</t>
+          <t>基于公开方向推测：处理遥感/雷达成像数据，复现实验中的滤波、检测或目标识别模块；复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -531,7 +611,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -541,30 +621,50 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/chenping9/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>data\raw_html\陈萍_32ff71596a.html</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>data\raw_text\陈萍_32ff71596a.txt</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -618,7 +718,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：围绕检测/识别/分割论文做复现，对公开图像或视频数据集做标注、训练和误差分析；处理遥感/雷达成像数据，复现实验中的滤波、检测或目标识别模块；整理多模态数据和提示词实验，复现视觉语言模型基线并做案例分析</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -653,30 +753,50 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向明显相关</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/liangkun/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>data\raw_html\梁琨_50d58e9f68.html</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>data\raw_text\梁琨_50d58e9f68.txt</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -730,7 +850,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：处理遥感/雷达成像数据，复现实验中的滤波、检测或目标识别模块；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -755,7 +875,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -765,30 +885,50 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/chenke/index.htm</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>data\raw_html\陈柯_6a62404523.html</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>data\raw_text\陈柯_6a62404523.txt</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -877,30 +1017,50 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>本科生接纳信息不足；公开页面产出线索较少；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/hefeng/</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>data\raw_html\贺锋_0dce7760f1.html</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>data\raw_text\贺锋_0dce7760f1.txt</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>页面可读取文本较少，建议人工打开原始HTML或来源URL核验。</t>
         </is>
@@ -954,7 +1114,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -979,7 +1139,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -989,30 +1149,50 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/zhangjing/</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>data\raw_html\张靖_14714bfbf4.html</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>data\raw_text\张靖_14714bfbf4.txt</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1066,7 +1246,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读</t>
+          <t>基于公开方向推测：先做 3-5 篇代表性论文精读，整理术语表、数据集和可复现实验清单</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1091,7 +1271,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1101,30 +1281,50 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；有一定论文/项目线索；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/zhoubo/</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>data\raw_html\周波_ea883f9c1a.html</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>data\raw_text\周波_ea883f9c1a.txt</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1178,7 +1378,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；硬件测试、仿真建模、实验平台辅助</t>
+          <t>基于公开方向推测：处理遥感/雷达成像数据，复现实验中的滤波、检测或目标识别模块；复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；做硬件平台资料整理、测试脚本、FPGA/嵌入式小模块或实验记录自动化</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1203,7 +1403,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1213,30 +1413,50 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/tianjiasheng</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>data\raw_html\田加胜_3e108a8f19.html</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>data\raw_text\田加胜_3e108a8f19.txt</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1290,7 +1510,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：处理遥感/雷达成像数据，复现实验中的滤波、检测或目标识别模块；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1315,7 +1535,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1325,30 +1545,50 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/jinjiang/</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>data\raw_html\金江_557bafb51e.html</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>data\raw_text\金江_557bafb51e.txt</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1402,7 +1642,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：围绕检测/识别/分割论文做复现，对公开图像或视频数据集做标注、训练和误差分析；处理遥感/雷达成像数据，复现实验中的滤波、检测或目标识别模块；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1437,30 +1677,50 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/huangquanliang/</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>data\raw_html\黄全亮_1481165afe.html</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>data\raw_text\黄全亮_1481165afe.txt</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1514,7 +1774,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1529,7 +1789,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t/>
+          <t>数据挖掘</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1539,7 +1799,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1549,30 +1809,50 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；有一定论文/项目线索；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/zhanghua/</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>data\raw_html\张华_8455ae09ee.html</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>data\raw_text\张华_8455ae09ee.txt</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1661,30 +1941,50 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>本科生接纳信息不足；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/zhudong/</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>data\raw_html\朱冬_6744056529.html</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>data\raw_text\朱冬_6744056529.txt</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1738,7 +2038,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；硬件测试、仿真建模、实验平台辅助；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；做硬件平台资料整理、测试脚本、FPGA/嵌入式小模块或实验记录自动化；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1773,30 +2073,50 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；公开页面产出线索较少；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/liuminggang/</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>data\raw_html\刘明罡_93e94083d8.html</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>data\raw_text\刘明罡_93e94083d8.txt</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1850,7 +2170,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读</t>
+          <t>基于公开方向推测：先做 3-5 篇代表性论文精读，整理术语表、数据集和可复现实验清单</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1875,7 +2195,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1885,30 +2205,50 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/sujinlong1/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/dzgcx.htm</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>data\raw_html\苏金龙_642b5f5f1e.html</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>data\raw_text\苏金龙_642b5f5f1e.txt</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1962,7 +2302,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1997,30 +2337,50 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/qiucaiming/</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>data\raw_html\邱才明_7131bd1b9c.html</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>data\raw_text\邱才明_7131bd1b9c.txt</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2074,7 +2434,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2099,7 +2459,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2109,30 +2469,50 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/gexiaohu/index.html</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>data\raw_html\葛晓虎_d517989935.html</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>data\raw_text\葛晓虎_d517989935.txt</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2186,7 +2566,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2211,7 +2591,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2221,30 +2601,50 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/liuyingzhuang/index.htm</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>data\raw_html\刘应状_bc538b70e5.html</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>data\raw_text\刘应状_bc538b70e5.txt</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2298,7 +2698,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；硬件测试、仿真建模、实验平台辅助；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；做硬件平台资料整理、测试脚本、FPGA/嵌入式小模块或实验记录自动化；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2323,7 +2723,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2333,30 +2733,50 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/qudaiming/index.html</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>data\raw_html\屈代明_47568e80e3.html</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>data\raw_text\屈代明_47568e80e3.txt</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2410,7 +2830,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2435,7 +2855,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2445,30 +2865,50 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/dongyan/index.htm</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>data\raw_html\董燕_3de3524627.html</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>data\raw_text\董燕_3de3524627.txt</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2557,30 +2997,50 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>主页抓取失败，三个维度均需人工核验。</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
           <t>https://faculty.hust.edu.cn/wei/zh_CN/index/750969/list/index.htm</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>data\raw_html\王巍_c49e77e0fe.html</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>data\raw_text\王巍_c49e77e0fe.txt</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>请求或解析失败：&lt;urlopen error _ssl.c:1063: The handshake operation timed out&gt;</t>
         </is>
@@ -2634,7 +3094,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析</t>
+          <t>基于公开方向推测：复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2649,7 +3109,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>机器学习；人工智能；detection；vision；machine learning</t>
+          <t>机器学习；人工智能；detection；vision；machine learning；知识图谱；强化学习</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2659,7 +3119,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2669,30 +3129,50 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/xiaoyong/index.html</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>data\raw_html\肖泳_542fb32e8b.html</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>data\raw_text\肖泳_542fb32e8b.txt</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2771,7 +3251,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2781,30 +3261,50 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/yin</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>data\raw_html\尹海帆_a602d8aae1.html</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>data\raw_text\尹海帆_a602d8aae1.txt</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2893,30 +3393,50 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>本科生接纳信息不足；公开页面产出线索较少；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/wangdesheng/</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>data\raw_html\王德胜_96fd4b905a.html</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>data\raw_text\王德胜_96fd4b905a.txt</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>页面可读取文本较少，建议人工打开原始HTML或来源URL核验。</t>
         </is>
@@ -2970,7 +3490,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2995,7 +3515,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3005,30 +3525,50 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向明显相关</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/hantao</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>data\raw_html\韩涛_ea2abc2903.html</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>data\raw_text\韩涛_ea2abc2903.txt</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3082,7 +3622,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读</t>
+          <t>基于公开方向推测：先做 3-5 篇代表性论文精读，整理术语表、数据集和可复现实验清单</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3107,7 +3647,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3117,30 +3657,50 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/pengwei1/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>data\raw_html\彭薇_7d2a18136c.html</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>data\raw_text\彭薇_7d2a18136c.txt</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3194,7 +3754,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3209,7 +3769,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>深度学习；人工智能；deep learning</t>
+          <t>深度学习；人工智能；deep learning；强化学习</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3219,7 +3779,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3229,30 +3789,50 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/liqiang/</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>data\raw_html\李强_e180f0fd10.html</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>data\raw_text\李强_e180f0fd10.txt</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3341,30 +3921,50 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>本科生接纳信息不足；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/wankai/</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>data\raw_html\万凯_5f60560da7.html</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>data\raw_text\万凯_5f60560da7.txt</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3418,7 +4018,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：围绕检测/识别/分割论文做复现，对公开图像或视频数据集做标注、训练和误差分析；复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3443,7 +4043,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3453,30 +4053,50 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/caoyang/</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>data\raw_html\曹洋_6a779ec4ef.html</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>data\raw_text\曹洋_6a779ec4ef.txt</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3530,7 +4150,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读</t>
+          <t>基于公开方向推测：先做 3-5 篇代表性论文精读，整理术语表、数据集和可复现实验清单</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3555,7 +4175,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3565,30 +4185,50 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；公开页面产出线索较少；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/~rQZfM3/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>data\raw_html\周桂_0c0f2971f5.html</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>data\raw_text\周桂_0c0f2971f5.txt</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3642,7 +4282,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读</t>
+          <t>基于公开方向推测：先做 3-5 篇代表性论文精读，整理术语表、数据集和可复现实验清单</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3657,7 +4297,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>模式识别</t>
+          <t>模式识别；智能系统</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3677,30 +4317,50 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；公开页面产出线索较少；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/chenwang/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>data\raw_html\王琛_3724aef4bc.html</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>data\raw_text\王琛_3724aef4bc.txt</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3754,7 +4414,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3779,7 +4439,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3789,30 +4449,50 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/xuzhengguang/</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>data\raw_html\徐争光_cd04b60dd2.html</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>data\raw_text\徐争光_cd04b60dd2.txt</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3866,7 +4546,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；安全论文阅读、实验复现、工具链整理；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；复现安全论文实验，整理数据集、攻击/防御流程和评测指标；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3901,30 +4581,50 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；公开页面产出线索较少；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/huangbenxiong/</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>data\raw_html\黄本雄_b58b6d5611.html</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>data\raw_text\黄本雄_b58b6d5611.txt</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3978,7 +4678,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4003,7 +4703,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4013,30 +4713,50 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/wuweimin/</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>data\raw_html\吴伟民_8d7ae772b0.html</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>data\raw_text\吴伟民_8d7ae772b0.txt</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4090,7 +4810,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4115,7 +4835,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4125,30 +4845,50 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/wangfei/</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>data\raw_html\王非_59d1d7fcf1.html</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>data\raw_text\王非_59d1d7fcf1.txt</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4202,7 +4942,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4227,7 +4967,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4237,30 +4977,50 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/daibin/</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>data\raw_html\戴彬_a91ab288f1.html</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>data\raw_text\戴彬_a91ab288f1.txt</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4314,7 +5074,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4339,7 +5099,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4349,30 +5109,50 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/heixiaojun/</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>data\raw_html\黑晓军_286cc78cfd.html</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>data\raw_text\黑晓军_286cc78cfd.txt</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4426,7 +5206,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4451,7 +5231,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4461,30 +5241,50 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/tangzuping/</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>data\raw_html\唐祖平_b0d0575831.html</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>data\raw_text\唐祖平_b0d0575831.txt</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4538,7 +5338,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4563,7 +5363,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4573,30 +5373,50 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/humenglan/humenglan.html</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>data\raw_html\胡梦兰_c64c22b11d.html</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>data\raw_text\胡梦兰_c64c22b11d.txt</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4685,30 +5505,50 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>本科生接纳信息不足；公开页面产出线索较少；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/lufang/</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>data\raw_html\鲁放_af08c5a0f0.html</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>data\raw_text\鲁放_af08c5a0f0.txt</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>页面可读取文本较少，建议人工打开原始HTML或来源URL核验。</t>
         </is>
@@ -4762,7 +5602,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；硬件测试、仿真建模、实验平台辅助；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；做硬件平台资料整理、测试脚本、FPGA/嵌入式小模块或实验记录自动化；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4787,7 +5627,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4797,30 +5637,50 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/tanli1/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>data\raw_html\谭力_e6b06789b1.html</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>data\raw_text\谭力_e6b06789b1.txt</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4874,7 +5734,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析</t>
+          <t>基于公开方向推测：复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4899,7 +5759,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4909,30 +5769,50 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/gaoyayu/</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>data\raw_html\高雅玙_84761e3509.html</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>data\raw_text\高雅玙_84761e3509.txt</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5021,30 +5901,50 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>本科生接纳信息不足；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/liaozhenyu/</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>data\raw_html\廖振宇_ef2d3d03bb.html</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>data\raw_text\廖振宇_ef2d3d03bb.txt</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5098,7 +5998,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5123,7 +6023,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5133,30 +6033,50 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/zhongyi/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>data\raw_html\钟祎_a7a19836cc.html</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>data\raw_text\钟祎_a7a19836cc.txt</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5210,7 +6130,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5235,7 +6155,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5245,30 +6165,50 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/chenda/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>data\raw_html\陈达_0d4cc7b551.html</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>data\raw_text\陈达_0d4cc7b551.txt</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5322,7 +6262,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读</t>
+          <t>基于公开方向推测：先做 3-5 篇代表性论文精读，整理术语表、数据集和可复现实验清单</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5337,7 +6277,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>人工智能</t>
+          <t>人工智能；智能优化</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5347,7 +6287,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5357,30 +6297,50 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/YeJunliang/zh_CN/more/2538182/jsjjgd/index.htm</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/txgcx.htm</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>data\raw_html\叶俊良_0be08597fe.html</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>data\raw_text\叶俊良_0be08597fe.txt</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5434,7 +6394,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；安全论文阅读、实验复现、工具链整理</t>
+          <t>基于公开方向推测：复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；复现安全论文实验，整理数据集、攻击/防御流程和评测指标</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5459,7 +6419,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5469,30 +6429,50 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/chengwenqing/</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>data\raw_html\程文青_b7993c31ff.html</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>data\raw_text\程文青_b7993c31ff.txt</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5546,7 +6526,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：围绕检测/识别/分割论文做复现，对公开图像或视频数据集做标注、训练和误差分析；复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5581,30 +6561,50 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向明显相关</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/liuwenyu/</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>data\raw_html\刘文予_fc33b2bd14.html</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>data\raw_text\刘文予_fc33b2bd14.txt</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5693,30 +6693,50 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>本科生接纳信息不足；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/yuli/</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>data\raw_html\喻莉_37c1ee1381.html</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>data\raw_text\喻莉_37c1ee1381.txt</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5770,7 +6790,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测</t>
+          <t>基于公开方向推测：复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5795,7 +6815,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5805,30 +6825,50 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/tianyan/</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>data\raw_html\田岩_c586741230.html</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>data\raw_text\田岩_c586741230.txt</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5882,7 +6922,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读</t>
+          <t>基于公开方向推测：先做 3-5 篇代表性论文精读，整理术语表、数据集和可复现实验清单</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5907,7 +6947,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5917,30 +6957,50 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；有一定论文/项目线索；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/wangbang/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>data\raw_html\王邦_97294bb022.html</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>data\raw_text\王邦_97294bb022.txt</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5994,7 +7054,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；安全论文阅读、实验复现、工具链整理</t>
+          <t>基于公开方向推测：复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；复现安全论文实验，整理数据集、攻击/防御流程和评测指标</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -6019,7 +7079,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6029,30 +7089,50 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/pengkai/pengkai.html</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>data\raw_html\彭凯_331a9acf82.html</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>data\raw_text\彭凯_331a9acf82.txt</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6106,7 +7186,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；做硬件平台资料整理、测试脚本、FPGA/嵌入式小模块或实验记录自动化；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -6131,7 +7211,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6141,30 +7221,50 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/zhuming</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>data\raw_html\朱明_cc4ee1c6d3.html</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>data\raw_text\朱明_cc4ee1c6d3.txt</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6253,30 +7353,50 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>主页抓取失败，三个维度均需人工核验。</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
           <t>https://faculty.hust.edu.cn/wliu/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>data\raw_html\刘威_da273f9df8.html</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>data\raw_text\刘威_da273f9df8.txt</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>请求或解析失败：&lt;urlopen error _ssl.c:1063: The handshake operation timed out&gt;</t>
         </is>
@@ -6330,7 +7450,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -6355,7 +7475,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6365,30 +7485,50 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/guopeng/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>data\raw_html\郭鹏_333f432e36.html</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>data\raw_text\郭鹏_333f432e36.txt</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6442,7 +7582,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测</t>
+          <t>基于公开方向推测：围绕检测/识别/分割论文做复现，对公开图像或视频数据集做标注、训练和误差分析；整理医学影像数据处理流程，复现分割/诊断模型并做可视化评估；复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -6477,30 +7617,50 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/yangxin/</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>data\raw_html\杨欣_68534739ff.html</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>data\raw_text\杨欣_68534739ff.txt</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6554,7 +7714,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；安全论文阅读、实验复现、工具链整理</t>
+          <t>基于公开方向推测：围绕检测/识别/分割论文做复现，对公开图像或视频数据集做标注、训练和误差分析；整理医学影像数据处理流程，复现分割/诊断模型并做可视化评估；整理多模态数据和提示词实验，复现视觉语言模型基线并做案例分析</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6589,30 +7749,50 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向明显相关</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/yangyou/</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>data\raw_html\杨铀_72de3b2d8a.html</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>data\raw_text\杨铀_72de3b2d8a.txt</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6701,30 +7881,50 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>本科生接纳信息不足；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/professor/liuqiong/</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>data\raw_html\刘琼_f3faee0e20.html</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>data\raw_text\刘琼_f3faee0e20.txt</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6778,7 +7978,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读</t>
+          <t>基于公开方向推测：先做 3-5 篇代表性论文精读，整理术语表、数据集和可复现实验清单</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6803,7 +8003,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6813,30 +8013,50 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/xwang/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>data\raw_html\王兴刚_ce79d9cf25.html</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>data\raw_text\王兴刚_ce79d9cf25.txt</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6890,7 +8110,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读</t>
+          <t>基于公开方向推测：先做 3-5 篇代表性论文精读，整理术语表、数据集和可复现实验清单</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6925,30 +8145,50 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向明显相关</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/chengqimin/</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>data\raw_html\程起敏_5aaaa4e184.html</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>data\raw_text\程起敏_5aaaa4e184.txt</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7002,7 +8242,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -7017,7 +8257,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>图像识别；多模态；recognition</t>
+          <t>图像识别；多模态；recognition；强化学习</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7027,7 +8267,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7037,30 +8277,50 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/fengbin1/zh_CN/index/1489780/list/index.htm</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>data\raw_html\冯镔_a40389f56d.html</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>data\raw_text\冯镔_a40389f56d.txt</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7114,7 +8374,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测</t>
+          <t>基于公开方向推测：围绕检测/识别/分割论文做复现，对公开图像或视频数据集做标注、训练和误差分析</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -7139,7 +8399,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7149,30 +8409,50 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向可能相关</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/yuzhou</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>data\raw_html\周瑜_de5d87e3bb.html</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>data\raw_text\周瑜_de5d87e3bb.txt</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7261,30 +8541,50 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>本科生接纳信息不足；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/huanghaojun/index.html</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>data\raw_html\黄浩军_ddbe770cfe.html</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>data\raw_text\黄浩军_ddbe770cfe.txt</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7338,7 +8638,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析</t>
+          <t>基于公开方向推测：复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -7363,7 +8663,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7373,30 +8673,50 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/xujing/</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="V66" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>data\raw_html\徐晶_e41ed9c6c7.html</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>data\raw_text\徐晶_e41ed9c6c7.txt</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7485,30 +8805,50 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>本科生接纳信息不足；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/yangpeng/index.html</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>data\raw_html\杨鹏_7b4e00e988.html</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>data\raw_text\杨鹏_7b4e00e988.txt</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7597,30 +8937,50 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>本科生接纳信息不足；公开页面产出线索较少；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/xuyiping/</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>data\raw_html\许毅平_ee0617a5c5.html</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>data\raw_text\许毅平_ee0617a5c5.txt</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>页面可读取文本较少，建议人工打开原始HTML或来源URL核验。</t>
         </is>
@@ -7674,7 +9034,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；安全论文阅读、实验复现、工具链整理；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：围绕检测/识别/分割论文做复现，对公开图像或视频数据集做标注、训练和误差分析；整理医学影像数据处理流程，复现分割/诊断模型并做可视化评估；复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -7709,30 +9069,50 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向明显相关</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
           <t>http://eic.hust.edu.cn/aprofessor/xuduanquan/index.htm</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>data\raw_html\徐端全_ec2570c65e.html</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>data\raw_text\徐端全_ec2570c65e.txt</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7786,7 +9166,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测</t>
+          <t>基于公开方向推测：围绕检测/识别/分割论文做复现，对公开图像或视频数据集做标注、训练和误差分析；整理多模态数据和提示词实验，复现视觉语言模型基线并做案例分析；复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7821,30 +9201,50 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向明显相关</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/xuwei7/zh_CN/index/1711225/list/index.htm</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>data\raw_html\许炜_20ec034a20.html</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>data\raw_text\许炜_20ec034a20.txt</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7898,7 +9298,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：围绕检测/识别/分割论文做复现，对公开图像或视频数据集做标注、训练和误差分析；整理医学影像数据处理流程，复现分割/诊断模型并做可视化评估；复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7923,7 +9323,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7933,30 +9333,50 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向明显相关</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/yanzengqiang/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>data\raw_html\闫增强_dd3d812553.html</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>data\raw_text\闫增强_dd3d812553.txt</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8010,7 +9430,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；做硬件平台资料整理、测试脚本、FPGA/嵌入式小模块或实验记录自动化；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -8035,7 +9455,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8045,30 +9465,50 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；有一定论文/项目线索；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/dengtian2/zh_CN/index.htm</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="V72" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>data\raw_html\邓田_da2373561e.html</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>data\raw_text\邓田_da2373561e.txt</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8122,7 +9562,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析</t>
+          <t>基于公开方向推测：围绕检测/识别/分割论文做复现，对公开图像或视频数据集做标注、训练和误差分析；复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -8137,7 +9577,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>计算机视觉；模式识别；人工智能；image；video；vision</t>
+          <t>计算机视觉；模式识别；人工智能；image；video；vision；智能系统</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8157,30 +9597,50 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>公开文本中出现本科生/竞赛/实习等友好信号；论文或项目产出线索较多；与 AI/智能方向明显相关</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/XianKe/zh_CN/index/2541862/list/index.htm</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="V73" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>data\raw_html\鲜可_91badb9b43.html</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>data\raw_text\鲜可_91badb9b43.txt</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8234,7 +9694,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读</t>
+          <t>基于公开方向推测：先做 3-5 篇代表性论文精读，整理术语表、数据集和可复现实验清单</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -8249,7 +9709,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>人工智能；多模态；大模型</t>
+          <t>人工智能；多模态；大模型；智能系统</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8259,7 +9719,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8269,30 +9729,50 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/LiuGaoyang/zh_CN/index/2616394/list/index.htm</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="V74" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>data\raw_html\刘高扬_e327d37bae.html</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>data\raw_text\刘高扬_e327d37bae.txt</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8371,7 +9851,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8381,30 +9861,50 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；论文或项目产出线索较多；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
           <t>http://faculty.hust.edu.cn/WuKejun</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="V75" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/xxgcx.htm</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>data\raw_html\吴科君_f4ca0c50f7.html</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>data\raw_text\吴科君_f4ca0c50f7.txt</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8458,7 +9958,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>推测：文献阅读与论文精读；算法复现、数据处理、模型评测；通信/信号处理仿真、实验数据分析；原型系统开发、脚本工具与工程实现</t>
+          <t>基于公开方向推测：复现机器学习/深度学习基线，做消融实验、参数对比和结果可视化；搭建通信或信号处理仿真脚本，分析频谱/信道/传输实验数据；开发小型实验工具、数据处理脚本、Web 可视化或原型系统模块</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -8483,7 +9983,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8493,30 +9993,50 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>有团队/项目/招生线索，但本科生接纳需核验；有一定论文/项目线索；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
           <t>http://ei.hust.edu.cn/professor/wangxiaoyan/</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/jxsyzx.htm</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>data\raw_html\汪小燕_12d64fb221.html</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>data\raw_text\汪小燕_12d64fb221.txt</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8605,30 +10125,50 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>本科生接纳信息不足；公开页面产出线索较少；与 AI/智能方向相关性较弱或待核验</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
           <t>http://ei.hust.edu.cn/professor/dengtianping/</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="V77" t="inlineStr">
         <is>
           <t>https://eic.hust.edu.cn/xygk/szdw/jxsyzx.htm</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="W77" t="inlineStr">
         <is>
           <t>data\raw_html\邓天平_a5cdced3d2.html</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>data\raw_text\邓天平_a5cdced3d2.txt</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>页面可读取文本较少，建议人工打开原始HTML或来源URL核验。</t>
         </is>
